--- a/jinni_knowledge/price_list_current.xlsx
+++ b/jinni_knowledge/price_list_current.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vladdnk/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48C548AA-25A6-B84F-BAD8-E098C2604DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FF7C92-EAB9-7442-91B6-BA2294B0C079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33260" yWindow="3800" windowWidth="28800" windowHeight="16140" xr2:uid="{9A498A90-5C26-CD4D-B471-173A37E36DA0}"/>
+    <workbookView xWindow="-33260" yWindow="3780" windowWidth="28800" windowHeight="16140" xr2:uid="{9A498A90-5C26-CD4D-B471-173A37E36DA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="200">
   <si>
     <t>Категория</t>
   </si>
@@ -590,9 +590,6 @@
     <t>Финишный монтаж инженерного оборудования</t>
   </si>
   <si>
-    <t xml:space="preserve"> дверей</t>
-  </si>
-  <si>
     <t>Чистовой монтаж смесителя и леек душа</t>
   </si>
   <si>
@@ -632,10 +629,13 @@
     <t>Финишный монтаж инженерного оборудования  дверей</t>
   </si>
   <si>
-    <t>Финишный монтаж инженерного оборудования  дверей Чистовой монтаж смесителя и леек душа</t>
-  </si>
-  <si>
-    <t>Финишный монтаж инженерного оборудования дверей Чистовой монтаж смесителя гигиенического душа</t>
+    <t>цена материала</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Чистовой монтаж смесителя гигиенического душа</t>
+  </si>
+  <si>
+    <t>м п</t>
   </si>
 </sst>
 </file>
@@ -1020,9 +1020,10 @@
     <col min="1" max="1" width="81.83203125" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1035,8 +1036,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1049,8 +1053,11 @@
       <c r="D2" s="1">
         <v>7500</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1063,8 +1070,11 @@
       <c r="D3" s="1">
         <v>2500</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1077,8 +1087,11 @@
       <c r="D4" s="1">
         <v>7400</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1091,8 +1104,11 @@
       <c r="D5" s="1">
         <v>200</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1105,8 +1121,11 @@
       <c r="D6" s="1">
         <v>204</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1119,8 +1138,11 @@
       <c r="D7" s="1">
         <v>1690</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1155,11 @@
       <c r="D8" s="1">
         <v>1790</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1147,8 +1172,11 @@
       <c r="D9" s="1">
         <v>2040</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -1161,8 +1189,11 @@
       <c r="D10" s="1">
         <v>408</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -1175,8 +1206,11 @@
       <c r="D11" s="1">
         <v>204</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -1189,8 +1223,11 @@
       <c r="D12" s="1">
         <v>1020</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -1203,8 +1240,11 @@
       <c r="D13" s="1">
         <v>340</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1217,8 +1257,11 @@
       <c r="D14" s="1">
         <v>1220</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -1231,8 +1274,11 @@
       <c r="D15" s="1">
         <v>611</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -1245,8 +1291,11 @@
       <c r="D16" s="1">
         <v>1090</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -1259,8 +1308,11 @@
       <c r="D17" s="1">
         <v>883</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -1273,8 +1325,11 @@
       <c r="D18" s="1">
         <v>643</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1287,8 +1342,11 @@
       <c r="D19" s="1">
         <v>150</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -1301,8 +1359,11 @@
       <c r="D20" s="1">
         <v>24460</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -1315,8 +1376,11 @@
       <c r="D21" s="1">
         <v>8150</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -1329,8 +1393,11 @@
       <c r="D22" s="1">
         <v>6110</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>28</v>
       </c>
@@ -1343,8 +1410,11 @@
       <c r="D23" s="1">
         <v>6790</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
@@ -1357,8 +1427,11 @@
       <c r="D24" s="1">
         <v>21740</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -1371,8 +1444,11 @@
       <c r="D25" s="1">
         <v>7470</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>28</v>
       </c>
@@ -1385,8 +1461,11 @@
       <c r="D26" s="1">
         <v>6500</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -1399,8 +1478,11 @@
       <c r="D27" s="1">
         <v>7500</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
@@ -1413,8 +1495,11 @@
       <c r="D28" s="1">
         <v>9000</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -1427,8 +1512,11 @@
       <c r="D29" s="1">
         <v>611</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -1441,8 +1529,11 @@
       <c r="D30" s="1">
         <v>217</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
@@ -1455,8 +1546,11 @@
       <c r="D31" s="1">
         <v>476</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -1469,8 +1563,11 @@
       <c r="D32" s="1">
         <v>50000</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>38</v>
       </c>
@@ -1483,8 +1580,11 @@
       <c r="D33" s="1">
         <v>15550</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>38</v>
       </c>
@@ -1497,8 +1597,11 @@
       <c r="D34" s="1">
         <v>2000</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
@@ -1511,8 +1614,11 @@
       <c r="D35" s="1">
         <v>4500</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>47</v>
       </c>
@@ -1525,8 +1631,11 @@
       <c r="D36" s="1">
         <v>204</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>47</v>
       </c>
@@ -1539,8 +1648,11 @@
       <c r="D37" s="1">
         <v>711</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>47</v>
       </c>
@@ -1553,8 +1665,11 @@
       <c r="D38" s="1">
         <v>204</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>47</v>
       </c>
@@ -1567,8 +1682,11 @@
       <c r="D39" s="1">
         <v>743</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>47</v>
       </c>
@@ -1581,8 +1699,11 @@
       <c r="D40" s="1">
         <v>1190</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>53</v>
       </c>
@@ -1595,8 +1716,11 @@
       <c r="D41" s="1">
         <v>4500</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>53</v>
       </c>
@@ -1609,8 +1733,11 @@
       <c r="D42" s="1">
         <v>4900</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>53</v>
       </c>
@@ -1623,8 +1750,11 @@
       <c r="D43" s="1">
         <v>5000</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>53</v>
       </c>
@@ -1637,8 +1767,11 @@
       <c r="D44" s="1">
         <v>450</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>53</v>
       </c>
@@ -1651,8 +1784,11 @@
       <c r="D45" s="1">
         <v>250</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>53</v>
       </c>
@@ -1665,8 +1801,11 @@
       <c r="D46" s="1">
         <v>1100</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -1679,8 +1818,11 @@
       <c r="D47" s="1">
         <v>150</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
@@ -1693,8 +1835,11 @@
       <c r="D48" s="1">
         <v>600</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>62</v>
       </c>
@@ -1707,8 +1852,11 @@
       <c r="D49" s="1">
         <v>7440</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>62</v>
       </c>
@@ -1721,8 +1869,11 @@
       <c r="D50" s="1">
         <v>2770</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>62</v>
       </c>
@@ -1735,8 +1886,11 @@
       <c r="D51" s="1">
         <v>2040</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>62</v>
       </c>
@@ -1749,8 +1903,11 @@
       <c r="D52" s="1">
         <v>950</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>62</v>
       </c>
@@ -1763,8 +1920,11 @@
       <c r="D53" s="1">
         <v>14700</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>62</v>
       </c>
@@ -1777,8 +1937,11 @@
       <c r="D54" s="1">
         <v>7400</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>62</v>
       </c>
@@ -1791,8 +1954,11 @@
       <c r="D55" s="1">
         <v>4700</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
@@ -1805,8 +1971,11 @@
       <c r="D56" s="1">
         <v>1470</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>62</v>
       </c>
@@ -1819,8 +1988,11 @@
       <c r="D57" s="1">
         <v>4700</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>62</v>
       </c>
@@ -1833,8 +2005,16 @@
       <c r="D58" s="1">
         <v>27500</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>75</v>
       </c>
@@ -1847,8 +2027,11 @@
       <c r="D60" s="2">
         <v>250</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>75</v>
       </c>
@@ -1861,8 +2044,11 @@
       <c r="D61" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>75</v>
       </c>
@@ -1875,8 +2061,11 @@
       <c r="D62" s="2">
         <v>120</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>75</v>
       </c>
@@ -1889,8 +2078,11 @@
       <c r="D63" s="2">
         <v>950</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>75</v>
       </c>
@@ -1903,8 +2095,11 @@
       <c r="D64" s="2">
         <v>750</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>75</v>
       </c>
@@ -1917,8 +2112,11 @@
       <c r="D65" s="2">
         <v>1500</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>75</v>
       </c>
@@ -1931,8 +2129,11 @@
       <c r="D66" s="2">
         <v>1000</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>75</v>
       </c>
@@ -1945,8 +2146,11 @@
       <c r="D67" s="2">
         <v>850</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>85</v>
       </c>
@@ -1959,8 +2163,11 @@
       <c r="D68" s="2">
         <v>2500</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>85</v>
       </c>
@@ -1973,8 +2180,11 @@
       <c r="D69" s="2">
         <v>850</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E69" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>85</v>
       </c>
@@ -1987,8 +2197,11 @@
       <c r="D70" s="2">
         <v>400</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E70" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>88</v>
       </c>
@@ -2001,8 +2214,11 @@
       <c r="D71" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>88</v>
       </c>
@@ -2015,8 +2231,11 @@
       <c r="D72" s="2">
         <v>850</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>88</v>
       </c>
@@ -2029,8 +2248,11 @@
       <c r="D73" s="2">
         <v>2200</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>88</v>
       </c>
@@ -2043,8 +2265,11 @@
       <c r="D74" s="2">
         <v>4000</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>88</v>
       </c>
@@ -2057,8 +2282,11 @@
       <c r="D75" s="2">
         <v>850</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>88</v>
       </c>
@@ -2071,8 +2299,11 @@
       <c r="D76" s="2">
         <v>14100</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>88</v>
       </c>
@@ -2085,8 +2316,11 @@
       <c r="D77" s="2">
         <v>7500</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>95</v>
       </c>
@@ -2099,8 +2333,11 @@
       <c r="D78" s="2">
         <v>800</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>95</v>
       </c>
@@ -2113,8 +2350,11 @@
       <c r="D79" s="2">
         <v>400</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>95</v>
       </c>
@@ -2127,8 +2367,11 @@
       <c r="D80" s="2">
         <v>2700</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>95</v>
       </c>
@@ -2141,8 +2384,11 @@
       <c r="D81" s="2">
         <v>2600</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>100</v>
       </c>
@@ -2155,8 +2401,11 @@
       <c r="D82" s="2">
         <v>8000</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>100</v>
       </c>
@@ -2169,8 +2418,11 @@
       <c r="D83" s="2">
         <v>8000</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>100</v>
       </c>
@@ -2183,8 +2435,11 @@
       <c r="D84" s="2">
         <v>16500</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>100</v>
       </c>
@@ -2197,8 +2452,11 @@
       <c r="D85" s="2">
         <v>25000</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E85" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>107</v>
       </c>
@@ -2211,8 +2469,11 @@
       <c r="D86" s="2">
         <v>750</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>107</v>
       </c>
@@ -2225,8 +2486,11 @@
       <c r="D87" s="2">
         <v>450</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>107</v>
       </c>
@@ -2239,8 +2503,11 @@
       <c r="D88" s="2">
         <v>150</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>107</v>
       </c>
@@ -2253,8 +2520,11 @@
       <c r="D89" s="2">
         <v>900</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>107</v>
       </c>
@@ -2267,8 +2537,11 @@
       <c r="D90" s="2">
         <v>500</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>107</v>
       </c>
@@ -2281,14 +2554,20 @@
       <c r="D91" s="2">
         <v>4000</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>115</v>
       </c>
@@ -2301,8 +2580,11 @@
       <c r="D93">
         <v>300</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>115</v>
       </c>
@@ -2315,8 +2597,11 @@
       <c r="D94">
         <v>6000</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>115</v>
       </c>
@@ -2329,8 +2614,11 @@
       <c r="D95">
         <v>150</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>115</v>
       </c>
@@ -2343,8 +2631,11 @@
       <c r="D96">
         <v>400</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>115</v>
       </c>
@@ -2357,8 +2648,11 @@
       <c r="D97">
         <v>850</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>115</v>
       </c>
@@ -2371,8 +2665,11 @@
       <c r="D98">
         <v>700</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>115</v>
       </c>
@@ -2385,8 +2682,11 @@
       <c r="D99">
         <v>1700</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>115</v>
       </c>
@@ -2399,8 +2699,11 @@
       <c r="D100">
         <v>1900</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>115</v>
       </c>
@@ -2413,8 +2716,11 @@
       <c r="D101">
         <v>1800</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -2427,8 +2733,11 @@
       <c r="D102">
         <v>280</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2441,8 +2750,11 @@
       <c r="D103">
         <v>550</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>115</v>
       </c>
@@ -2455,8 +2767,11 @@
       <c r="D104">
         <v>2200</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>115</v>
       </c>
@@ -2469,8 +2784,11 @@
       <c r="D105">
         <v>450</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>115</v>
       </c>
@@ -2483,10 +2801,13 @@
       <c r="D106">
         <v>5000</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B107" t="s">
         <v>132</v>
@@ -2497,10 +2818,13 @@
       <c r="D107">
         <v>611</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B108" t="s">
         <v>133</v>
@@ -2511,10 +2835,13 @@
       <c r="D108">
         <v>250</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B109" t="s">
         <v>131</v>
@@ -2525,10 +2852,13 @@
       <c r="D109">
         <v>580</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B110" t="s">
         <v>131</v>
@@ -2539,10 +2869,13 @@
       <c r="D110">
         <v>23500</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B111" t="s">
         <v>131</v>
@@ -2553,10 +2886,13 @@
       <c r="D111">
         <v>6500</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B112" t="s">
         <v>131</v>
@@ -2567,10 +2903,13 @@
       <c r="D112">
         <v>3500</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B113" t="s">
         <v>131</v>
@@ -2581,10 +2920,13 @@
       <c r="D113">
         <v>7500</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B114" t="s">
         <v>131</v>
@@ -2595,10 +2937,13 @@
       <c r="D114">
         <v>5000</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B115" t="s">
         <v>131</v>
@@ -2609,10 +2954,13 @@
       <c r="D115">
         <v>5000</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B116" t="s">
         <v>131</v>
@@ -2623,10 +2971,13 @@
       <c r="D116">
         <v>1500</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B117" t="s">
         <v>131</v>
@@ -2637,8 +2988,11 @@
       <c r="D117">
         <v>5000</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>134</v>
       </c>
@@ -2651,8 +3005,11 @@
       <c r="D118">
         <v>2200</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>134</v>
       </c>
@@ -2665,8 +3022,11 @@
       <c r="D119">
         <v>8500</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>134</v>
       </c>
@@ -2679,8 +3039,11 @@
       <c r="D120">
         <v>500</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>138</v>
       </c>
@@ -2693,8 +3056,11 @@
       <c r="D121">
         <v>250</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>138</v>
       </c>
@@ -2707,8 +3073,11 @@
       <c r="D122">
         <v>204</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>138</v>
       </c>
@@ -2721,8 +3090,11 @@
       <c r="D123">
         <v>150</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>138</v>
       </c>
@@ -2735,8 +3107,11 @@
       <c r="D124">
         <v>1300</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>138</v>
       </c>
@@ -2749,8 +3124,11 @@
       <c r="D125">
         <v>1300</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>138</v>
       </c>
@@ -2763,8 +3141,11 @@
       <c r="D126">
         <v>204</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>138</v>
       </c>
@@ -2777,8 +3158,11 @@
       <c r="D127">
         <v>850</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>138</v>
       </c>
@@ -2791,8 +3175,11 @@
       <c r="D128">
         <v>450</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>138</v>
       </c>
@@ -2805,8 +3192,11 @@
       <c r="D129">
         <v>204</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>138</v>
       </c>
@@ -2819,8 +3209,11 @@
       <c r="D130">
         <v>5000</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>148</v>
       </c>
@@ -2833,8 +3226,11 @@
       <c r="D131">
         <v>5000</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>148</v>
       </c>
@@ -2847,8 +3243,11 @@
       <c r="D132">
         <v>12000</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>148</v>
       </c>
@@ -2861,8 +3260,11 @@
       <c r="D133">
         <v>6500</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>152</v>
       </c>
@@ -2875,8 +3277,11 @@
       <c r="D134">
         <v>4500</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>152</v>
       </c>
@@ -2889,8 +3294,11 @@
       <c r="D135">
         <v>4900</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>152</v>
       </c>
@@ -2903,8 +3311,11 @@
       <c r="D136">
         <v>12000</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>152</v>
       </c>
@@ -2917,8 +3328,11 @@
       <c r="D137">
         <v>2500</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>152</v>
       </c>
@@ -2931,8 +3345,11 @@
       <c r="D138">
         <v>1200</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>152</v>
       </c>
@@ -2945,8 +3362,11 @@
       <c r="D139">
         <v>1000</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>159</v>
       </c>
@@ -2959,8 +3379,11 @@
       <c r="D140">
         <v>150</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>159</v>
       </c>
@@ -2973,8 +3396,11 @@
       <c r="D141">
         <v>1150</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>159</v>
       </c>
@@ -2987,8 +3413,11 @@
       <c r="D142">
         <v>150</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>159</v>
       </c>
@@ -3001,8 +3430,11 @@
       <c r="D143">
         <v>150</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>159</v>
       </c>
@@ -3015,8 +3447,11 @@
       <c r="D144">
         <v>700</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>159</v>
       </c>
@@ -3029,8 +3464,11 @@
       <c r="D145">
         <v>600</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>159</v>
       </c>
@@ -3043,8 +3481,11 @@
       <c r="D146">
         <v>5000</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>166</v>
       </c>
@@ -3057,8 +3498,11 @@
       <c r="D147">
         <v>500</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>166</v>
       </c>
@@ -3071,8 +3515,11 @@
       <c r="D148">
         <v>350</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>166</v>
       </c>
@@ -3085,8 +3532,11 @@
       <c r="D149">
         <v>550</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>166</v>
       </c>
@@ -3099,8 +3549,11 @@
       <c r="D150">
         <v>150</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>166</v>
       </c>
@@ -3113,8 +3566,11 @@
       <c r="D151">
         <v>960</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>166</v>
       </c>
@@ -3127,13 +3583,16 @@
       <c r="D152">
         <v>300</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>166</v>
       </c>
       <c r="B153" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C153" t="s">
         <v>173</v>
@@ -3141,8 +3600,11 @@
       <c r="D153">
         <v>3500</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>166</v>
       </c>
@@ -3155,8 +3617,11 @@
       <c r="D154">
         <v>1000</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>166</v>
       </c>
@@ -3169,8 +3634,11 @@
       <c r="D155">
         <v>1200</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>166</v>
       </c>
@@ -3183,8 +3651,11 @@
       <c r="D156">
         <v>4000</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>166</v>
       </c>
@@ -3197,8 +3668,11 @@
       <c r="D157">
         <v>1500</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>166</v>
       </c>
@@ -3211,8 +3685,11 @@
       <c r="D158">
         <v>900</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>166</v>
       </c>
@@ -3225,8 +3702,11 @@
       <c r="D159">
         <v>1200</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>166</v>
       </c>
@@ -3238,6 +3718,9 @@
       </c>
       <c r="D160">
         <v>1300</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
@@ -3253,6 +3736,9 @@
       <c r="D161">
         <v>350</v>
       </c>
+      <c r="E161">
+        <v>0</v>
+      </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
@@ -3267,73 +3753,76 @@
       <c r="D162">
         <v>1200</v>
       </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B163" t="s">
         <v>184</v>
       </c>
       <c r="C163" t="s">
-        <v>185</v>
-      </c>
-      <c r="D163" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D163">
+        <v>2500</v>
       </c>
       <c r="E163">
-        <v>3500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B164" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C164" t="s">
-        <v>186</v>
-      </c>
-      <c r="D164" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D164">
+        <v>2500</v>
       </c>
       <c r="E164">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B165" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C165" t="s">
-        <v>187</v>
-      </c>
-      <c r="D165" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D165">
+        <v>2500</v>
       </c>
       <c r="E165">
-        <v>4700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B166" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C166" t="s">
-        <v>188</v>
-      </c>
-      <c r="D166" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D166">
+        <v>2500</v>
       </c>
       <c r="E166">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
@@ -3341,16 +3830,16 @@
         <v>183</v>
       </c>
       <c r="B167" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C167" t="s">
-        <v>189</v>
-      </c>
-      <c r="D167" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D167">
+        <v>2500</v>
       </c>
       <c r="E167">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
@@ -3358,16 +3847,16 @@
         <v>183</v>
       </c>
       <c r="B168" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C168" t="s">
-        <v>190</v>
-      </c>
-      <c r="D168" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D168">
+        <v>2500</v>
       </c>
       <c r="E168">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
@@ -3375,16 +3864,16 @@
         <v>183</v>
       </c>
       <c r="B169" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C169" t="s">
-        <v>191</v>
-      </c>
-      <c r="D169" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D169">
+        <v>7300</v>
       </c>
       <c r="E169">
-        <v>7300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
@@ -3392,16 +3881,16 @@
         <v>183</v>
       </c>
       <c r="B170" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C170" t="s">
-        <v>192</v>
-      </c>
-      <c r="D170" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D170">
+        <v>800</v>
       </c>
       <c r="E170">
-        <v>800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
@@ -3409,16 +3898,16 @@
         <v>183</v>
       </c>
       <c r="B171" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C171" t="s">
-        <v>193</v>
-      </c>
-      <c r="D171" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D171">
+        <v>800</v>
       </c>
       <c r="E171">
-        <v>800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
@@ -3426,16 +3915,16 @@
         <v>183</v>
       </c>
       <c r="B172" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="C172" t="s">
-        <v>194</v>
-      </c>
-      <c r="D172" t="s">
-        <v>11</v>
+        <v>199</v>
+      </c>
+      <c r="D172">
+        <v>300</v>
       </c>
       <c r="E172">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
@@ -3443,16 +3932,16 @@
         <v>183</v>
       </c>
       <c r="B173" t="s">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="C173" t="s">
-        <v>129</v>
-      </c>
-      <c r="D173" t="s">
         <v>130</v>
       </c>
+      <c r="D173">
+        <v>5000</v>
+      </c>
       <c r="E173">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
